--- a/storage/app/assessTemplate/condo.xlsx
+++ b/storage/app/assessTemplate/condo.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27231"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yokoyama\Desktop\火災見積\テンプレート\excel\評価シートテンプレート\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yokoyama\Desktop\修正用ふぉうるだ\assessTemplate\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B547FD2-8868-4592-B82B-D26EB08A395C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5AFE02C-9095-4E6B-8608-9A1C2A584DCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30" yWindow="750" windowWidth="28770" windowHeight="15450" xr2:uid="{32D26D25-8074-469B-B16E-A4F821DEBDDE}"/>
+    <workbookView xWindow="45" yWindow="45" windowWidth="28755" windowHeight="15435" xr2:uid="{32D26D25-8074-469B-B16E-A4F821DEBDDE}"/>
   </bookViews>
   <sheets>
     <sheet name="評価表（分譲マンション）" sheetId="2" r:id="rId1"/>
@@ -1143,6 +1143,14 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1152,48 +1160,40 @@
     <xf numFmtId="179" fontId="1" fillId="0" borderId="21" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="35" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="36" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="1" fillId="0" borderId="28" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="1" fillId="0" borderId="21" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="1" fillId="0" borderId="7" xfId="3" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="38" fontId="1" fillId="0" borderId="8" xfId="3" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="38" fontId="1" fillId="0" borderId="0" xfId="3" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="38" fontId="1" fillId="0" borderId="11" xfId="3" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="38" fontId="1" fillId="0" borderId="19" xfId="3" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="38" fontId="1" fillId="0" borderId="39" xfId="3" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="35" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="36" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="182" fontId="1" fillId="0" borderId="28" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="182" fontId="1" fillId="0" borderId="21" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="1" fillId="0" borderId="7" xfId="3" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="38" fontId="1" fillId="0" borderId="8" xfId="3" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
   </cellXfs>
@@ -1635,8 +1635,8 @@
       <c r="J7" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="K7" s="99"/>
-      <c r="L7" s="100"/>
+      <c r="K7" s="86"/>
+      <c r="L7" s="87"/>
       <c r="M7" s="16"/>
       <c r="N7" s="13"/>
     </row>
@@ -1742,11 +1742,11 @@
         <v>16</v>
       </c>
       <c r="C15" s="28"/>
-      <c r="D15" s="86" t="s">
+      <c r="D15" s="88" t="s">
         <v>17</v>
       </c>
-      <c r="E15" s="87"/>
-      <c r="F15" s="86" t="s">
+      <c r="E15" s="89"/>
+      <c r="F15" s="88" t="s">
         <v>18</v>
       </c>
       <c r="G15" s="29"/>
@@ -1762,9 +1762,9 @@
         <v>19</v>
       </c>
       <c r="C16" s="28"/>
-      <c r="D16" s="86"/>
-      <c r="E16" s="88"/>
-      <c r="F16" s="86"/>
+      <c r="D16" s="88"/>
+      <c r="E16" s="90"/>
+      <c r="F16" s="88"/>
       <c r="G16" s="33"/>
       <c r="H16" s="34"/>
       <c r="I16" s="31"/>
@@ -1778,9 +1778,9 @@
         <v>20</v>
       </c>
       <c r="C17" s="28"/>
-      <c r="D17" s="86"/>
-      <c r="E17" s="88"/>
-      <c r="F17" s="86"/>
+      <c r="D17" s="88"/>
+      <c r="E17" s="90"/>
+      <c r="F17" s="88"/>
       <c r="G17" s="35"/>
       <c r="H17" s="36"/>
       <c r="I17" s="31"/>
@@ -1805,10 +1805,10 @@
       <c r="E20" s="75" t="s">
         <v>22</v>
       </c>
-      <c r="G20" s="93" t="s">
+      <c r="G20" s="91" t="s">
         <v>23</v>
       </c>
-      <c r="H20" s="94"/>
+      <c r="H20" s="92"/>
       <c r="J20" s="77" t="s">
         <v>24</v>
       </c>
@@ -1836,11 +1836,11 @@
         <v>16</v>
       </c>
       <c r="C22" s="38"/>
-      <c r="D22" s="86" t="s">
+      <c r="D22" s="88" t="s">
         <v>17</v>
       </c>
-      <c r="E22" s="95"/>
-      <c r="F22" s="86" t="s">
+      <c r="E22" s="93"/>
+      <c r="F22" s="88" t="s">
         <v>18</v>
       </c>
       <c r="G22" s="39"/>
@@ -1856,9 +1856,9 @@
         <v>19</v>
       </c>
       <c r="C23" s="38"/>
-      <c r="D23" s="86"/>
-      <c r="E23" s="96"/>
-      <c r="F23" s="86"/>
+      <c r="D23" s="88"/>
+      <c r="E23" s="94"/>
+      <c r="F23" s="88"/>
       <c r="G23" s="42"/>
       <c r="H23" s="43"/>
       <c r="I23" s="41"/>
@@ -1872,9 +1872,9 @@
         <v>20</v>
       </c>
       <c r="C24" s="38"/>
-      <c r="D24" s="86"/>
-      <c r="E24" s="96"/>
-      <c r="F24" s="86"/>
+      <c r="D24" s="88"/>
+      <c r="E24" s="94"/>
+      <c r="F24" s="88"/>
       <c r="G24" s="44"/>
       <c r="H24" s="45"/>
       <c r="I24" s="41"/>
@@ -1907,84 +1907,84 @@
       <c r="A27" s="54" t="s">
         <v>26</v>
       </c>
-      <c r="B27" s="97"/>
-      <c r="C27" s="97"/>
-      <c r="D27" s="97"/>
-      <c r="E27" s="97"/>
-      <c r="F27" s="97"/>
-      <c r="G27" s="97"/>
-      <c r="H27" s="97"/>
-      <c r="I27" s="97"/>
-      <c r="J27" s="97"/>
-      <c r="K27" s="97"/>
-      <c r="L27" s="97"/>
-      <c r="M27" s="97"/>
-      <c r="N27" s="98"/>
+      <c r="B27" s="95"/>
+      <c r="C27" s="95"/>
+      <c r="D27" s="95"/>
+      <c r="E27" s="95"/>
+      <c r="F27" s="95"/>
+      <c r="G27" s="95"/>
+      <c r="H27" s="95"/>
+      <c r="I27" s="95"/>
+      <c r="J27" s="95"/>
+      <c r="K27" s="95"/>
+      <c r="L27" s="95"/>
+      <c r="M27" s="95"/>
+      <c r="N27" s="96"/>
       <c r="O27" s="55"/>
     </row>
     <row r="28" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A28" s="11"/>
-      <c r="B28" s="89"/>
-      <c r="C28" s="89"/>
-      <c r="D28" s="89"/>
-      <c r="E28" s="89"/>
-      <c r="F28" s="89"/>
-      <c r="G28" s="89"/>
-      <c r="H28" s="89"/>
-      <c r="I28" s="89"/>
-      <c r="J28" s="89"/>
-      <c r="K28" s="89"/>
-      <c r="L28" s="89"/>
-      <c r="M28" s="89"/>
-      <c r="N28" s="90"/>
+      <c r="B28" s="97"/>
+      <c r="C28" s="97"/>
+      <c r="D28" s="97"/>
+      <c r="E28" s="97"/>
+      <c r="F28" s="97"/>
+      <c r="G28" s="97"/>
+      <c r="H28" s="97"/>
+      <c r="I28" s="97"/>
+      <c r="J28" s="97"/>
+      <c r="K28" s="97"/>
+      <c r="L28" s="97"/>
+      <c r="M28" s="97"/>
+      <c r="N28" s="98"/>
     </row>
     <row r="29" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A29" s="11"/>
-      <c r="B29" s="89"/>
-      <c r="C29" s="89"/>
-      <c r="D29" s="89"/>
-      <c r="E29" s="89"/>
-      <c r="F29" s="89"/>
-      <c r="G29" s="89"/>
-      <c r="H29" s="89"/>
-      <c r="I29" s="89"/>
-      <c r="J29" s="89"/>
-      <c r="K29" s="89"/>
-      <c r="L29" s="89"/>
-      <c r="M29" s="89"/>
-      <c r="N29" s="90"/>
+      <c r="B29" s="97"/>
+      <c r="C29" s="97"/>
+      <c r="D29" s="97"/>
+      <c r="E29" s="97"/>
+      <c r="F29" s="97"/>
+      <c r="G29" s="97"/>
+      <c r="H29" s="97"/>
+      <c r="I29" s="97"/>
+      <c r="J29" s="97"/>
+      <c r="K29" s="97"/>
+      <c r="L29" s="97"/>
+      <c r="M29" s="97"/>
+      <c r="N29" s="98"/>
     </row>
     <row r="30" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A30" s="11"/>
-      <c r="B30" s="89"/>
-      <c r="C30" s="89"/>
-      <c r="D30" s="89"/>
-      <c r="E30" s="89"/>
-      <c r="F30" s="89"/>
-      <c r="G30" s="89"/>
-      <c r="H30" s="89"/>
-      <c r="I30" s="89"/>
-      <c r="J30" s="89"/>
-      <c r="K30" s="89"/>
-      <c r="L30" s="89"/>
-      <c r="M30" s="89"/>
-      <c r="N30" s="90"/>
+      <c r="B30" s="97"/>
+      <c r="C30" s="97"/>
+      <c r="D30" s="97"/>
+      <c r="E30" s="97"/>
+      <c r="F30" s="97"/>
+      <c r="G30" s="97"/>
+      <c r="H30" s="97"/>
+      <c r="I30" s="97"/>
+      <c r="J30" s="97"/>
+      <c r="K30" s="97"/>
+      <c r="L30" s="97"/>
+      <c r="M30" s="97"/>
+      <c r="N30" s="98"/>
     </row>
     <row r="31" spans="1:15" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A31" s="56"/>
-      <c r="B31" s="91"/>
-      <c r="C31" s="91"/>
-      <c r="D31" s="91"/>
-      <c r="E31" s="91"/>
-      <c r="F31" s="91"/>
-      <c r="G31" s="91"/>
-      <c r="H31" s="91"/>
-      <c r="I31" s="91"/>
-      <c r="J31" s="91"/>
-      <c r="K31" s="91"/>
-      <c r="L31" s="91"/>
-      <c r="M31" s="91"/>
-      <c r="N31" s="92"/>
+      <c r="B31" s="99"/>
+      <c r="C31" s="99"/>
+      <c r="D31" s="99"/>
+      <c r="E31" s="99"/>
+      <c r="F31" s="99"/>
+      <c r="G31" s="99"/>
+      <c r="H31" s="99"/>
+      <c r="I31" s="99"/>
+      <c r="J31" s="99"/>
+      <c r="K31" s="99"/>
+      <c r="L31" s="99"/>
+      <c r="M31" s="99"/>
+      <c r="N31" s="100"/>
     </row>
     <row r="32" spans="1:15" ht="26.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="E32" s="57"/>
@@ -2046,17 +2046,13 @@
     <row r="67" ht="18.75" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="73" ht="22.5" customHeight="1" x14ac:dyDescent="0.4"/>
   </sheetData>
-  <mergeCells count="32">
-    <mergeCell ref="B28:N28"/>
-    <mergeCell ref="B29:N29"/>
-    <mergeCell ref="B30:N30"/>
-    <mergeCell ref="B31:N31"/>
+  <mergeCells count="28">
+    <mergeCell ref="B27:N31"/>
     <mergeCell ref="G20:H20"/>
     <mergeCell ref="J20:K20"/>
     <mergeCell ref="D22:D24"/>
     <mergeCell ref="E22:E24"/>
     <mergeCell ref="F22:F24"/>
-    <mergeCell ref="B27:N27"/>
     <mergeCell ref="D15:D17"/>
     <mergeCell ref="E15:E17"/>
     <mergeCell ref="F15:F17"/>

--- a/storage/app/assessTemplate/condo.xlsx
+++ b/storage/app/assessTemplate/condo.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yokoyama\Desktop\修正用ふぉうるだ\assessTemplate\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-22.04\home\ohno\eruful\mitumo\storage\app\assessTemplate\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5AFE02C-9095-4E6B-8608-9A1C2A584DCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52DA6A67-6D4F-433F-97B4-FB0A70E73A28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="45" yWindow="45" windowWidth="28755" windowHeight="15435" xr2:uid="{32D26D25-8074-469B-B16E-A4F821DEBDDE}"/>
+    <workbookView xWindow="30225" yWindow="1425" windowWidth="24645" windowHeight="11295" xr2:uid="{32D26D25-8074-469B-B16E-A4F821DEBDDE}"/>
   </bookViews>
   <sheets>
     <sheet name="評価表（分譲マンション）" sheetId="2" r:id="rId1"/>
@@ -105,16 +105,6 @@
     <phoneticPr fontId="3"/>
   </si>
   <si>
-    <t>【延床面積】</t>
-    <rPh sb="1" eb="3">
-      <t>ノベユカ</t>
-    </rPh>
-    <rPh sb="3" eb="5">
-      <t>メンセキ</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
     <t>【築年数】</t>
     <rPh sb="1" eb="4">
       <t>チクネンスウユカメンセキ</t>
@@ -126,16 +116,6 @@
     <phoneticPr fontId="3"/>
   </si>
   <si>
-    <t>延床面積</t>
-    <rPh sb="0" eb="2">
-      <t>ノベユカ</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>メンセキ</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
     <t>再調達価額（100％）</t>
     <rPh sb="0" eb="3">
       <t>サイチョウタツ</t>
@@ -248,6 +228,26 @@
     <t>ダウンロード日</t>
     <rPh sb="6" eb="7">
       <t>ビ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>【専有面積】</t>
+    <rPh sb="1" eb="3">
+      <t>センユウ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>メンセキ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>専有面積</t>
+    <rPh sb="0" eb="2">
+      <t>センユウ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>メンセキ</t>
     </rPh>
     <phoneticPr fontId="3"/>
   </si>
@@ -1066,6 +1066,102 @@
     <xf numFmtId="38" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="38" fontId="1" fillId="0" borderId="7" xfId="3" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="38" fontId="1" fillId="0" borderId="8" xfId="3" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="38" fontId="1" fillId="0" borderId="0" xfId="3" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="38" fontId="1" fillId="0" borderId="11" xfId="3" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="38" fontId="1" fillId="0" borderId="19" xfId="3" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="38" fontId="1" fillId="0" borderId="39" xfId="3" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="35" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="36" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="22" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="23" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="1" fillId="0" borderId="28" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="1" fillId="0" borderId="21" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="1" fillId="0" borderId="28" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="1" fillId="0" borderId="21" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="20" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="24" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="3" borderId="21" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="3" borderId="25" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="40" fontId="7" fillId="0" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="40" fontId="7" fillId="0" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="58" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -1098,102 +1194,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="20" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="24" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="1" fillId="3" borderId="21" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="1" fillId="3" borderId="25" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="22" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="23" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="40" fontId="7" fillId="0" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="40" fontId="7" fillId="0" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="1" fillId="0" borderId="28" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="1" fillId="0" borderId="21" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="35" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="36" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="182" fontId="1" fillId="0" borderId="28" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="182" fontId="1" fillId="0" borderId="21" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="1" fillId="0" borderId="7" xfId="3" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="38" fontId="1" fillId="0" borderId="8" xfId="3" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="38" fontId="1" fillId="0" borderId="0" xfId="3" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="38" fontId="1" fillId="0" borderId="11" xfId="3" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="38" fontId="1" fillId="0" borderId="19" xfId="3" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="38" fontId="1" fillId="0" borderId="39" xfId="3" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
   </cellXfs>
@@ -1217,9 +1217,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office テーマ">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 テーマ">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1257,7 +1257,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1363,7 +1363,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1505,7 +1505,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1537,10 +1537,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="L1" s="64"/>
-      <c r="M1" s="64"/>
+      <c r="L1" s="92"/>
+      <c r="M1" s="92"/>
       <c r="N1" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="2" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.4">
@@ -1548,47 +1548,47 @@
       <c r="O2" s="3"/>
     </row>
     <row r="3" spans="1:15" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A3" s="65" t="s">
+      <c r="A3" s="93" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="65"/>
-      <c r="C3" s="65"/>
-      <c r="D3" s="65"/>
-      <c r="E3" s="65"/>
-      <c r="F3" s="65"/>
-      <c r="G3" s="65"/>
-      <c r="H3" s="65"/>
-      <c r="I3" s="65"/>
-      <c r="J3" s="65"/>
-      <c r="K3" s="65"/>
-      <c r="L3" s="65"/>
-      <c r="M3" s="65"/>
-      <c r="N3" s="65"/>
+      <c r="B3" s="93"/>
+      <c r="C3" s="93"/>
+      <c r="D3" s="93"/>
+      <c r="E3" s="93"/>
+      <c r="F3" s="93"/>
+      <c r="G3" s="93"/>
+      <c r="H3" s="93"/>
+      <c r="I3" s="93"/>
+      <c r="J3" s="93"/>
+      <c r="K3" s="93"/>
+      <c r="L3" s="93"/>
+      <c r="M3" s="93"/>
+      <c r="N3" s="93"/>
       <c r="O3" s="4"/>
     </row>
     <row r="4" spans="1:15" ht="32.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A4" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="66"/>
-      <c r="C4" s="67"/>
-      <c r="D4" s="67"/>
+      <c r="B4" s="94"/>
+      <c r="C4" s="95"/>
+      <c r="D4" s="95"/>
       <c r="E4" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="F4" s="68"/>
-      <c r="G4" s="69"/>
-      <c r="H4" s="69"/>
+      <c r="F4" s="96"/>
+      <c r="G4" s="97"/>
+      <c r="H4" s="97"/>
       <c r="I4" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="J4" s="70"/>
-      <c r="K4" s="71"/>
+      <c r="J4" s="98"/>
+      <c r="K4" s="99"/>
       <c r="L4" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="M4" s="68"/>
-      <c r="N4" s="72"/>
+      <c r="M4" s="96"/>
+      <c r="N4" s="100"/>
       <c r="O4" s="3"/>
     </row>
     <row r="5" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.4">
@@ -1596,8 +1596,8 @@
       <c r="B5" s="8"/>
       <c r="C5" s="8"/>
       <c r="D5" s="8"/>
-      <c r="E5" s="79"/>
-      <c r="F5" s="79"/>
+      <c r="E5" s="83"/>
+      <c r="F5" s="83"/>
       <c r="G5" s="9"/>
       <c r="H5" s="9"/>
       <c r="I5" s="9"/>
@@ -1616,27 +1616,27 @@
         <v>6</v>
       </c>
       <c r="H6" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="K6" s="12" t="s">
         <v>7</v>
-      </c>
-      <c r="K6" s="12" t="s">
-        <v>8</v>
       </c>
       <c r="L6" s="12"/>
       <c r="N6" s="13"/>
     </row>
     <row r="7" spans="1:15" ht="26.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A7" s="14"/>
-      <c r="B7" s="80"/>
-      <c r="C7" s="81"/>
-      <c r="E7" s="82"/>
-      <c r="F7" s="83"/>
-      <c r="H7" s="84"/>
-      <c r="I7" s="85"/>
+      <c r="B7" s="84"/>
+      <c r="C7" s="85"/>
+      <c r="E7" s="86"/>
+      <c r="F7" s="87"/>
+      <c r="H7" s="88"/>
+      <c r="I7" s="89"/>
       <c r="J7" s="15" t="s">
-        <v>9</v>
-      </c>
-      <c r="K7" s="86"/>
-      <c r="L7" s="87"/>
+        <v>8</v>
+      </c>
+      <c r="K7" s="90"/>
+      <c r="L7" s="91"/>
       <c r="M7" s="16"/>
       <c r="N7" s="13"/>
     </row>
@@ -1700,54 +1700,54 @@
     </row>
     <row r="13" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="11"/>
-      <c r="B13" s="73"/>
-      <c r="C13" s="73"/>
-      <c r="E13" s="75" t="s">
+      <c r="B13" s="79"/>
+      <c r="C13" s="79"/>
+      <c r="E13" s="81" t="s">
+        <v>27</v>
+      </c>
+      <c r="G13" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="H13" s="73"/>
+      <c r="I13" s="3"/>
+      <c r="J13" s="72" t="s">
         <v>10</v>
       </c>
-      <c r="G13" s="77" t="s">
-        <v>11</v>
-      </c>
-      <c r="H13" s="78"/>
-      <c r="I13" s="3"/>
-      <c r="J13" s="77" t="s">
-        <v>12</v>
-      </c>
-      <c r="K13" s="78"/>
+      <c r="K13" s="73"/>
       <c r="N13" s="13"/>
     </row>
     <row r="14" spans="1:15" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A14" s="11"/>
-      <c r="B14" s="74"/>
-      <c r="C14" s="74"/>
-      <c r="E14" s="76"/>
+      <c r="B14" s="80"/>
+      <c r="C14" s="80"/>
+      <c r="E14" s="82"/>
       <c r="G14" s="25" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H14" s="26" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I14" s="3"/>
       <c r="J14" s="25" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="K14" s="26" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="N14" s="13"/>
     </row>
     <row r="15" spans="1:15" ht="27.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
       <c r="A15" s="11"/>
       <c r="B15" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="C15" s="28"/>
+      <c r="D15" s="74" t="s">
+        <v>15</v>
+      </c>
+      <c r="E15" s="77"/>
+      <c r="F15" s="74" t="s">
         <v>16</v>
-      </c>
-      <c r="C15" s="28"/>
-      <c r="D15" s="88" t="s">
-        <v>17</v>
-      </c>
-      <c r="E15" s="89"/>
-      <c r="F15" s="88" t="s">
-        <v>18</v>
       </c>
       <c r="G15" s="29"/>
       <c r="H15" s="30"/>
@@ -1759,12 +1759,12 @@
     <row r="16" spans="1:15" ht="27.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="11"/>
       <c r="B16" s="32" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C16" s="28"/>
-      <c r="D16" s="88"/>
-      <c r="E16" s="90"/>
-      <c r="F16" s="88"/>
+      <c r="D16" s="74"/>
+      <c r="E16" s="78"/>
+      <c r="F16" s="74"/>
       <c r="G16" s="33"/>
       <c r="H16" s="34"/>
       <c r="I16" s="31"/>
@@ -1775,12 +1775,12 @@
     <row r="17" spans="1:15" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A17" s="11"/>
       <c r="B17" s="32" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C17" s="28"/>
-      <c r="D17" s="88"/>
-      <c r="E17" s="90"/>
-      <c r="F17" s="88"/>
+      <c r="D17" s="74"/>
+      <c r="E17" s="78"/>
+      <c r="F17" s="74"/>
       <c r="G17" s="35"/>
       <c r="H17" s="36"/>
       <c r="I17" s="31"/>
@@ -1798,50 +1798,50 @@
     </row>
     <row r="20" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="11"/>
-      <c r="B20" s="73"/>
-      <c r="C20" s="73" t="s">
+      <c r="B20" s="79"/>
+      <c r="C20" s="79" t="s">
+        <v>19</v>
+      </c>
+      <c r="E20" s="81" t="s">
+        <v>20</v>
+      </c>
+      <c r="G20" s="70" t="s">
         <v>21</v>
       </c>
-      <c r="E20" s="75" t="s">
+      <c r="H20" s="71"/>
+      <c r="J20" s="72" t="s">
         <v>22</v>
       </c>
-      <c r="G20" s="91" t="s">
-        <v>23</v>
-      </c>
-      <c r="H20" s="92"/>
-      <c r="J20" s="77" t="s">
-        <v>24</v>
-      </c>
-      <c r="K20" s="78"/>
+      <c r="K20" s="73"/>
       <c r="N20" s="13"/>
     </row>
     <row r="21" spans="1:15" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A21" s="11"/>
-      <c r="B21" s="74"/>
-      <c r="C21" s="74"/>
-      <c r="E21" s="76"/>
+      <c r="B21" s="80"/>
+      <c r="C21" s="80"/>
+      <c r="E21" s="82"/>
       <c r="G21" s="37"/>
       <c r="H21" s="26" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="J21" s="25"/>
       <c r="K21" s="26" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="N21" s="13"/>
     </row>
     <row r="22" spans="1:15" ht="27.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
       <c r="A22" s="11"/>
       <c r="B22" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="C22" s="38"/>
+      <c r="D22" s="74" t="s">
+        <v>15</v>
+      </c>
+      <c r="E22" s="75"/>
+      <c r="F22" s="74" t="s">
         <v>16</v>
-      </c>
-      <c r="C22" s="38"/>
-      <c r="D22" s="88" t="s">
-        <v>17</v>
-      </c>
-      <c r="E22" s="93"/>
-      <c r="F22" s="88" t="s">
-        <v>18</v>
       </c>
       <c r="G22" s="39"/>
       <c r="H22" s="40"/>
@@ -1853,12 +1853,12 @@
     <row r="23" spans="1:15" ht="27.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="11"/>
       <c r="B23" s="32" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C23" s="38"/>
-      <c r="D23" s="88"/>
-      <c r="E23" s="94"/>
-      <c r="F23" s="88"/>
+      <c r="D23" s="74"/>
+      <c r="E23" s="76"/>
+      <c r="F23" s="74"/>
       <c r="G23" s="42"/>
       <c r="H23" s="43"/>
       <c r="I23" s="41"/>
@@ -1869,12 +1869,12 @@
     <row r="24" spans="1:15" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A24" s="11"/>
       <c r="B24" s="32" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C24" s="38"/>
-      <c r="D24" s="88"/>
-      <c r="E24" s="94"/>
-      <c r="F24" s="88"/>
+      <c r="D24" s="74"/>
+      <c r="E24" s="76"/>
+      <c r="F24" s="74"/>
       <c r="G24" s="44"/>
       <c r="H24" s="45"/>
       <c r="I24" s="41"/>
@@ -1905,86 +1905,86 @@
     </row>
     <row r="27" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A27" s="54" t="s">
-        <v>26</v>
-      </c>
-      <c r="B27" s="95"/>
-      <c r="C27" s="95"/>
-      <c r="D27" s="95"/>
-      <c r="E27" s="95"/>
-      <c r="F27" s="95"/>
-      <c r="G27" s="95"/>
-      <c r="H27" s="95"/>
-      <c r="I27" s="95"/>
-      <c r="J27" s="95"/>
-      <c r="K27" s="95"/>
-      <c r="L27" s="95"/>
-      <c r="M27" s="95"/>
-      <c r="N27" s="96"/>
+        <v>24</v>
+      </c>
+      <c r="B27" s="64"/>
+      <c r="C27" s="64"/>
+      <c r="D27" s="64"/>
+      <c r="E27" s="64"/>
+      <c r="F27" s="64"/>
+      <c r="G27" s="64"/>
+      <c r="H27" s="64"/>
+      <c r="I27" s="64"/>
+      <c r="J27" s="64"/>
+      <c r="K27" s="64"/>
+      <c r="L27" s="64"/>
+      <c r="M27" s="64"/>
+      <c r="N27" s="65"/>
       <c r="O27" s="55"/>
     </row>
     <row r="28" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A28" s="11"/>
-      <c r="B28" s="97"/>
-      <c r="C28" s="97"/>
-      <c r="D28" s="97"/>
-      <c r="E28" s="97"/>
-      <c r="F28" s="97"/>
-      <c r="G28" s="97"/>
-      <c r="H28" s="97"/>
-      <c r="I28" s="97"/>
-      <c r="J28" s="97"/>
-      <c r="K28" s="97"/>
-      <c r="L28" s="97"/>
-      <c r="M28" s="97"/>
-      <c r="N28" s="98"/>
+      <c r="B28" s="66"/>
+      <c r="C28" s="66"/>
+      <c r="D28" s="66"/>
+      <c r="E28" s="66"/>
+      <c r="F28" s="66"/>
+      <c r="G28" s="66"/>
+      <c r="H28" s="66"/>
+      <c r="I28" s="66"/>
+      <c r="J28" s="66"/>
+      <c r="K28" s="66"/>
+      <c r="L28" s="66"/>
+      <c r="M28" s="66"/>
+      <c r="N28" s="67"/>
     </row>
     <row r="29" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A29" s="11"/>
-      <c r="B29" s="97"/>
-      <c r="C29" s="97"/>
-      <c r="D29" s="97"/>
-      <c r="E29" s="97"/>
-      <c r="F29" s="97"/>
-      <c r="G29" s="97"/>
-      <c r="H29" s="97"/>
-      <c r="I29" s="97"/>
-      <c r="J29" s="97"/>
-      <c r="K29" s="97"/>
-      <c r="L29" s="97"/>
-      <c r="M29" s="97"/>
-      <c r="N29" s="98"/>
+      <c r="B29" s="66"/>
+      <c r="C29" s="66"/>
+      <c r="D29" s="66"/>
+      <c r="E29" s="66"/>
+      <c r="F29" s="66"/>
+      <c r="G29" s="66"/>
+      <c r="H29" s="66"/>
+      <c r="I29" s="66"/>
+      <c r="J29" s="66"/>
+      <c r="K29" s="66"/>
+      <c r="L29" s="66"/>
+      <c r="M29" s="66"/>
+      <c r="N29" s="67"/>
     </row>
     <row r="30" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A30" s="11"/>
-      <c r="B30" s="97"/>
-      <c r="C30" s="97"/>
-      <c r="D30" s="97"/>
-      <c r="E30" s="97"/>
-      <c r="F30" s="97"/>
-      <c r="G30" s="97"/>
-      <c r="H30" s="97"/>
-      <c r="I30" s="97"/>
-      <c r="J30" s="97"/>
-      <c r="K30" s="97"/>
-      <c r="L30" s="97"/>
-      <c r="M30" s="97"/>
-      <c r="N30" s="98"/>
+      <c r="B30" s="66"/>
+      <c r="C30" s="66"/>
+      <c r="D30" s="66"/>
+      <c r="E30" s="66"/>
+      <c r="F30" s="66"/>
+      <c r="G30" s="66"/>
+      <c r="H30" s="66"/>
+      <c r="I30" s="66"/>
+      <c r="J30" s="66"/>
+      <c r="K30" s="66"/>
+      <c r="L30" s="66"/>
+      <c r="M30" s="66"/>
+      <c r="N30" s="67"/>
     </row>
     <row r="31" spans="1:15" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A31" s="56"/>
-      <c r="B31" s="99"/>
-      <c r="C31" s="99"/>
-      <c r="D31" s="99"/>
-      <c r="E31" s="99"/>
-      <c r="F31" s="99"/>
-      <c r="G31" s="99"/>
-      <c r="H31" s="99"/>
-      <c r="I31" s="99"/>
-      <c r="J31" s="99"/>
-      <c r="K31" s="99"/>
-      <c r="L31" s="99"/>
-      <c r="M31" s="99"/>
-      <c r="N31" s="100"/>
+      <c r="B31" s="68"/>
+      <c r="C31" s="68"/>
+      <c r="D31" s="68"/>
+      <c r="E31" s="68"/>
+      <c r="F31" s="68"/>
+      <c r="G31" s="68"/>
+      <c r="H31" s="68"/>
+      <c r="I31" s="68"/>
+      <c r="J31" s="68"/>
+      <c r="K31" s="68"/>
+      <c r="L31" s="68"/>
+      <c r="M31" s="68"/>
+      <c r="N31" s="69"/>
     </row>
     <row r="32" spans="1:15" ht="26.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="E32" s="57"/>
@@ -2047,34 +2047,34 @@
     <row r="73" ht="22.5" customHeight="1" x14ac:dyDescent="0.4"/>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="L1:M1"/>
+    <mergeCell ref="A3:N3"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="F4:H4"/>
+    <mergeCell ref="J4:K4"/>
+    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="B13:B14"/>
+    <mergeCell ref="C13:C14"/>
+    <mergeCell ref="E13:E14"/>
+    <mergeCell ref="G13:H13"/>
+    <mergeCell ref="J13:K13"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="H7:I7"/>
+    <mergeCell ref="K7:L7"/>
+    <mergeCell ref="D15:D17"/>
+    <mergeCell ref="E15:E17"/>
+    <mergeCell ref="F15:F17"/>
+    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="C20:C21"/>
+    <mergeCell ref="E20:E21"/>
     <mergeCell ref="B27:N31"/>
     <mergeCell ref="G20:H20"/>
     <mergeCell ref="J20:K20"/>
     <mergeCell ref="D22:D24"/>
     <mergeCell ref="E22:E24"/>
     <mergeCell ref="F22:F24"/>
-    <mergeCell ref="D15:D17"/>
-    <mergeCell ref="E15:E17"/>
-    <mergeCell ref="F15:F17"/>
-    <mergeCell ref="B20:B21"/>
-    <mergeCell ref="C20:C21"/>
-    <mergeCell ref="E20:E21"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="H7:I7"/>
-    <mergeCell ref="K7:L7"/>
-    <mergeCell ref="B13:B14"/>
-    <mergeCell ref="C13:C14"/>
-    <mergeCell ref="E13:E14"/>
-    <mergeCell ref="G13:H13"/>
-    <mergeCell ref="J13:K13"/>
-    <mergeCell ref="L1:M1"/>
-    <mergeCell ref="A3:N3"/>
-    <mergeCell ref="B4:D4"/>
-    <mergeCell ref="F4:H4"/>
-    <mergeCell ref="J4:K4"/>
-    <mergeCell ref="M4:N4"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <dataValidations count="1">
